--- a/Luban/Data/#uiform.xlsx
+++ b/Luban/Data/#uiform.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LiteGame/UI/Screens/UIMain.prefab</t>
+          <t>UI/Screens/UIMain.prefab</t>
         </is>
       </c>
       <c r="E4" t="n">
